--- a/public/modelo-diario.xlsx
+++ b/public/modelo-diario.xlsx
@@ -555,7 +555,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Preencha a partir da linha 5. A linha 4, em amarelo, é um exemplo — APAGUE-A antes de importar. Só a coluna “Atividade / Detalhes” é obrigatória; linha sem ela é ignorada. Não mude os nomes das colunas: é por eles que o MILEST reconhece cada campo.</t>
+          <t>Preencha a partir da linha 5. A linha 4, em amarelo, é só um exemplo do formato — pode apagá-la, e se esquecer o sistema a ignora. Só a coluna “Atividade / Detalhes” é obrigatória; linha sem ela é ignorada. Não mude os nomes das colunas: é por eles que o MILEST reconhece cada campo.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>P-1</t>
+          <t>EXEMPLO</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -3114,7 +3114,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Apague a linha 4 (o exemplo em amarelo) antes de importar.</t>
+          <t>A linha 4, em amarelo, é o exemplo do formato. Pode apagar — e se esquecer, o sistema a ignora pelo ID “EXEMPLO”.</t>
         </is>
       </c>
     </row>
@@ -3124,14 +3124,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2. Selecione da linha 3 (o cabeçalho) até a última linha preenchida e copie (Ctrl/Cmd+C).</t>
+          <t>2. Copie as linhas, OU salve esta aba como .csv — tanto faz.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>O cabeçalho precisa ir junto: é por ele que o sistema reconhece cada coluna.</t>
+          <t>Se for copiar, inclua a linha 3 (o cabeçalho). Se salvar como .csv, salve a planilha inteira: o sistema acha o cabeçalho sozinho.</t>
         </is>
       </c>
     </row>
